--- a/balancete_receita.xlsx
+++ b/balancete_receita.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDB05C88-83EE-4910-BDA3-699D8CF69AEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{826DAD11-43BD-45E9-8F65-817BEED81161}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="balancete_receita" sheetId="1" r:id="rId1"/>
+    <sheet name="balancete_receita_SJC" sheetId="1" r:id="rId1"/>
     <sheet name="tipo_despesa" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="416">
   <si>
     <t>Ano</t>
   </si>
@@ -1265,13 +1265,19 @@
     <t>Dedução de Receita para Formação do Fundeb - IPI</t>
   </si>
   <si>
-    <t>Valor no mês de fevereiro</t>
+    <t>Tipo de receita</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1755,10 +1761,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1804,7 +1811,29 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1815,6 +1844,1016 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tipo_despesa!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Valor </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>tipo_despesa!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>IMPOSTOS, TAXAS E CONTRIBUIÇÕES DE MELHORIA</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CONTRIBUIÇÕES</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RECEITA PATRIMONIAL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TRANSFERÊNCIAS CORRENTES</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>OUTRAS RECEITAS CORRENTES</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>tipo_despesa!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>283700636.22000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4006044.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>234963.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>187826199.84</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14982524.390000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6FB9-45E9-93DE-20CDC64ECD8B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="267"/>
+        <c:overlap val="-43"/>
+        <c:axId val="1041738608"/>
+        <c:axId val="1040499552"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1041738608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1040499552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1040499552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1041738608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="208">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81689EB9-C918-496F-9DCA-1B1B578F2778}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1832,6 +2871,19 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Receita Orçada (R$)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F5C430F-BE53-480D-931E-D35A815D0688}" name="Tabela2" displayName="Tabela2" ref="A1:B6" totalsRowShown="0">
+  <autoFilter ref="A1:B6" xr:uid="{98B7F457-E4F0-4EA6-9DF7-A00E7C3B7549}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{D2077B52-6BF2-4F7A-A691-CAC32A20FA02}" name="Tipo de receita" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{ECE69078-23CF-446B-A3F3-20598494F3C0}" name="Valor" dataDxfId="0">
+      <calculatedColumnFormula>VLOOKUP(A2,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -13526,38 +14578,62 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
         <v>414</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="3">
+        <f>VLOOKUP(A2,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</f>
+        <v>283700636.22000003</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="B3" s="3">
+        <f>VLOOKUP(A3,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</f>
+        <v>4006044.96</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="B4" s="3">
+        <f>VLOOKUP(A4,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</f>
+        <v>234963.91</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>214</v>
       </c>
+      <c r="B5" s="3">
+        <f>VLOOKUP(A5,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</f>
+        <v>187826199.84</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>318</v>
       </c>
+      <c r="B6" s="3">
+        <f>VLOOKUP(A6,Tabela1[[#All],[Receita]:[Receita Orçada (R$)]],2,FALSE)</f>
+        <v>14982524.390000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>